--- a/reports/pdf_change_20260831.xlsx
+++ b/reports/pdf_change_20260831.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억   ·   현금 33억(0.7%)      당일 2026-08-31  vs  전영업일 2026-08-28      매수 2종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억      당일 2026-08-31  vs  전영업일 2026-08-28      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -779,7 +779,7 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,961억   ·   현금 12억(0.3%)      당일 2026-08-31  vs  전영업일 2026-08-28      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,961억      당일 2026-08-31  vs  전영업일 2026-08-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -803,7 +803,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,614억   ·   현금 36억(1.4%)      당일 2026-08-31  vs  전영업일 2026-08-28      매수 2종목  /  매도 1종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,614억      당일 2026-08-31  vs  전영업일 2026-08-28      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -964,7 +964,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,251억   ·   현금 27억(1.2%)      당일 2026-08-31  vs  전영업일 2026-08-28      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,251억      당일 2026-08-31  vs  전영업일 2026-08-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -988,7 +988,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 278억   ·   현금 2억(0.7%)      당일 2026-08-31  vs  전영업일 2026-08-28      매수 5종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 278억      당일 2026-08-31  vs  전영업일 2026-08-28      매수 5종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1274,23 +1274,23 @@
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스엔비티</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-26863200</v>
+        <v>-4520880</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>1.20%→1.10%</t>
+          <t>0.54%→0.52%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>86→79</t>
+          <t>229→222</t>
         </is>
       </c>
     </row>
@@ -1302,23 +1302,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>코스맥스엔비티</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-4520880</v>
+        <v>-26863200</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>0.54%→0.52%</t>
+          <t>1.20%→1.10%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>229→222</t>
+          <t>86→79</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 566억   ·   현금 3억(0.5%)      당일 2026-08-31  vs  전영업일 2026-08-28      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 566억      당일 2026-08-31  vs  전영업일 2026-08-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>

--- a/reports/pdf_change_20260831.xlsx
+++ b/reports/pdf_change_20260831.xlsx
@@ -1274,23 +1274,23 @@
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>코스맥스엔비티</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-4520880</v>
+        <v>-26863200</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.54%→0.52%</t>
+          <t>1.20%→1.10%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>229→222</t>
+          <t>86→79</t>
         </is>
       </c>
     </row>
@@ -1302,23 +1302,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스엔비티</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-26863200</v>
+        <v>-4520880</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>1.20%→1.10%</t>
+          <t>0.54%→0.52%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>86→79</t>
+          <t>229→222</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260831.xlsx
+++ b/reports/pdf_change_20260831.xlsx
@@ -1274,23 +1274,23 @@
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스엔비티</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-26863200</v>
+        <v>-4520880</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>1.20%→1.10%</t>
+          <t>0.54%→0.52%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>86→79</t>
+          <t>229→222</t>
         </is>
       </c>
     </row>
@@ -1302,23 +1302,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>코스맥스엔비티</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-4520880</v>
+        <v>-26863200</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>0.54%→0.52%</t>
+          <t>1.20%→1.10%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>229→222</t>
+          <t>86→79</t>
         </is>
       </c>
     </row>
